--- a/SİLİFKE.xlsx
+++ b/SİLİFKE.xlsx
@@ -458,7 +458,7 @@
         <v>Yol</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I2" t="str">
         <v/>
@@ -467,7 +467,7 @@
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
       <c r="K2" t="str">
-        <v/>
+        <v>2026-04-07</v>
       </c>
     </row>
     <row r="3">
